--- a/pauta_verificador_pcsp.xlsx
+++ b/pauta_verificador_pcsp.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-27 17:15:38</t>
+          <t>2026-05-27 17:54:33</t>
         </is>
       </c>
     </row>

--- a/pauta_verificador_pcsp.xlsx
+++ b/pauta_verificador_pcsp.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-01 11:35:21</t>
+          <t>2026-06-01 15:45:30</t>
         </is>
       </c>
     </row>
